--- a/programme/chair-sheets/S21.xlsx
+++ b/programme/chair-sheets/S21.xlsx
@@ -46,19 +46,19 @@
     <t xml:space="preserve">Session chair</t>
   </si>
   <si>
+    <t xml:space="preserve">K. Naga Maha Lakshmi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Co-chair</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dr. Bazani Shaik</t>
   </si>
   <si>
-    <t xml:space="preserve">Co-chair</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
     <t xml:space="preserve">Joining link</t>
   </si>
   <si>
-    <t xml:space="preserve">to be confirmed</t>
+    <t xml:space="preserve">https://meet.google.com/jjg-skto-rev</t>
   </si>
   <si>
     <t xml:space="preserve">#</t>
